--- a/Results/RILUZOLE_vs_MND_RILUZOLE.xlsx
+++ b/Results/RILUZOLE_vs_MND_RILUZOLE.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RILUZOLE</t>
+          <t>RILUZOLE PLACEBO</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MND RILUZOLE</t>
+          <t>RILUZOLE MND</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>56.75 ± 10.99</t>
+          <t>56.00 ± 11.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1709</v>
+        <v>0.0756</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.12 ± 0.25</t>
+          <t>0.11 ± 0.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,7 +519,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.5476</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>376 (40.1%)</t>
+          <t>89 (37.4%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>562 (59.9%)</t>
+          <t>149 (62.6%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>43 (4.6%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>895 (95.4%)</t>
+          <t>238 (100.0%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
